--- a/sample_data/customer_request_filled.xlsx
+++ b/sample_data/customer_request_filled.xlsx
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1. Customer &amp; sample (Request form - sheet 1)</t>
+          <t>Request form - Sheet 1</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2. Request form - sheet 2</t>
+          <t>Request form - Sheet 2</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>3. Proforma for transformers (manufacturer-declared data)</t>
+          <t>Proforma for transformers</t>
         </is>
       </c>
     </row>
